--- a/vermont_results/statewide/republican/rep_lieutenant_governor.xlsx
+++ b/vermont_results/statewide/republican/rep_lieutenant_governor.xlsx
@@ -2964,7 +2964,7 @@
         <v>94</v>
       </c>
       <c r="E98" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F98" t="n">
         <v>109</v>
@@ -5044,7 +5044,7 @@
         <v>189</v>
       </c>
       <c r="E178" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F178" t="n">
         <v>219</v>
@@ -5374,7 +5374,7 @@
         <v>19961</v>
       </c>
       <c r="E191" t="n">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F191" t="n">
         <v>22753</v>

--- a/vermont_results/statewide/republican/rep_lieutenant_governor.xlsx
+++ b/vermont_results/statewide/republican/rep_lieutenant_governor.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F247"/>
+  <dimension ref="A1:F248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2626,7 +2626,7 @@
         <v>50</v>
       </c>
       <c r="E85" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F85" t="n">
         <v>60</v>
@@ -3935,220 +3935,220 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NEWPORT CITY</t>
+          <t>NEWFANE</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ORLEANS-2</t>
+          <t>WINDHAM-5</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>ESSEX_</t>
+          <t>WINDHAM_</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>110</v>
+        <v>61</v>
       </c>
       <c r="E136" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F136" t="n">
-        <v>124</v>
+        <v>71</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>NEWPORT TOWN</t>
+          <t>NEWPORT CITY</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ORLEANS LAMOILLE</t>
+          <t>ORLEANS-2</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>ORLEANS_</t>
+          <t>ESSEX_</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="E137" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F137" t="n">
-        <v>69</v>
+        <v>124</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NORTH HERO</t>
+          <t>NEWPORT TOWN</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GRAND ISLE CHITTENDEN</t>
+          <t>ORLEANS LAMOILLE</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>GRAND ISLE_</t>
+          <t>ORLEANS_</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E138" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F138" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>NORTHFIELD</t>
+          <t>NORTH HERO</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>WASHINGTON-1</t>
+          <t>GRAND ISLE CHITTENDEN</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>WASHINGTON_</t>
+          <t>GRAND ISLE_</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>165</v>
+        <v>49</v>
       </c>
       <c r="E139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F139" t="n">
-        <v>187</v>
+        <v>57</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NORTON</t>
+          <t>NORTHFIELD</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ESSEX ORLEANS</t>
+          <t>WASHINGTON-1</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>ESSEX_</t>
+          <t>WASHINGTON_</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>18</v>
+        <v>165</v>
       </c>
       <c r="E140" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F140" t="n">
-        <v>19</v>
+        <v>187</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NORWICH</t>
+          <t>NORTON</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>WINDSOR ORANGE 2</t>
+          <t>ESSEX ORLEANS</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>WINDSOR_</t>
+          <t>ESSEX_</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
       </c>
       <c r="F141" t="n">
-        <v>44</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ORANGE</t>
+          <t>NORWICH</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ORANGE-1</t>
+          <t>WINDSOR ORANGE 2</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>WASHINGTON_</t>
+          <t>WINDSOR_</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="E142" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F142" t="n">
-        <v>82</v>
+        <v>44</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ORWELL</t>
+          <t>ORANGE</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ADDISON RUTLAND</t>
+          <t>ORANGE-1</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>ADDISON_</t>
+          <t>WASHINGTON_</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="E143" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F143" t="n">
-        <v>134</v>
+        <v>82</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PANTON</t>
+          <t>ORWELL</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ADDISON-3</t>
+          <t>ADDISON RUTLAND</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4157,206 +4157,206 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>31</v>
+        <v>114</v>
       </c>
       <c r="E144" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F144" t="n">
-        <v>33</v>
+        <v>134</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>PAWLET</t>
+          <t>PANTON</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>RUTLAND BENNINGTON</t>
+          <t>ADDISON-3</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>RUTLAND_</t>
+          <t>ADDISON_</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="E145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F145" t="n">
-        <v>82</v>
+        <v>33</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>PEACHAM</t>
+          <t>PAWLET</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CALEDONIA WASHINGTON</t>
+          <t>RUTLAND BENNINGTON</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CALEDONIA_</t>
+          <t>RUTLAND_</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="E146" t="n">
         <v>0</v>
       </c>
       <c r="F146" t="n">
-        <v>39</v>
+        <v>82</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PERU</t>
+          <t>PEACHAM</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>BENNINGTON RUTLAND</t>
+          <t>CALEDONIA WASHINGTON</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>BENNINGTON_</t>
+          <t>CALEDONIA_</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="E147" t="n">
         <v>0</v>
       </c>
       <c r="F147" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PITTSFIELD</t>
+          <t>PERU</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>RUTLAND-11</t>
+          <t>BENNINGTON RUTLAND</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>WINDSOR_</t>
+          <t>BENNINGTON_</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E148" t="n">
         <v>0</v>
       </c>
       <c r="F148" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PITTSFORD</t>
+          <t>PITTSFIELD</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>RUTLAND-8</t>
+          <t>RUTLAND-11</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>RUTLAND_</t>
+          <t>WINDSOR_</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>104</v>
+        <v>23</v>
       </c>
       <c r="E149" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F149" t="n">
-        <v>112</v>
+        <v>26</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PLAINFIELD</t>
+          <t>PITTSFORD</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>WASHINGTON-6</t>
+          <t>RUTLAND-8</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>WASHINGTON_</t>
+          <t>RUTLAND_</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>34</v>
+        <v>104</v>
       </c>
       <c r="E150" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F150" t="n">
-        <v>40</v>
+        <v>112</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PLYMOUTH</t>
+          <t>PLAINFIELD</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>WINDSOR-5</t>
+          <t>WASHINGTON-6</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>WINDSOR_</t>
+          <t>WASHINGTON_</t>
         </is>
       </c>
       <c r="D151" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F151" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>POMFRET</t>
+          <t>PLYMOUTH</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>WINDSOR-4</t>
+          <t>WINDSOR-5</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4365,284 +4365,284 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E152" t="n">
         <v>1</v>
       </c>
       <c r="F152" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>POULTNEY</t>
+          <t>POMFRET</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>RUTLAND-1</t>
+          <t>WINDSOR-4</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>RUTLAND_</t>
+          <t>WINDSOR_</t>
         </is>
       </c>
       <c r="D153" t="n">
-        <v>137</v>
+        <v>25</v>
       </c>
       <c r="E153" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F153" t="n">
-        <v>155</v>
+        <v>27</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>POWNAL</t>
+          <t>POULTNEY</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>BENNINGTON-1, BENNINGTON-5</t>
+          <t>RUTLAND-1</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>BENNINGTON_</t>
+          <t>RUTLAND_</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="E154" t="n">
         <v>3</v>
       </c>
       <c r="F154" t="n">
-        <v>159</v>
+        <v>155</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PROCTOR</t>
+          <t>POWNAL</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>RUTLAND-8</t>
+          <t>BENNINGTON-1, BENNINGTON-5</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>RUTLAND_</t>
+          <t>BENNINGTON_</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="E155" t="n">
         <v>3</v>
       </c>
       <c r="F155" t="n">
-        <v>56</v>
+        <v>159</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PUTNEY</t>
+          <t>PROCTOR</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>WINDHAM-4</t>
+          <t>RUTLAND-8</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>WINDHAM_</t>
+          <t>RUTLAND_</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="E156" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F156" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>RANDOLPH</t>
+          <t>PUTNEY</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ORANGE WASHINGTON ADDISON</t>
+          <t>WINDHAM-4</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>ORANGE_</t>
+          <t>WINDHAM_</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>123</v>
+        <v>26</v>
       </c>
       <c r="E157" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F157" t="n">
-        <v>146</v>
+        <v>30</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>READING</t>
+          <t>RANDOLPH</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>WINDSOR-5</t>
+          <t>ORANGE WASHINGTON ADDISON</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>WINDSOR_</t>
+          <t>ORANGE_</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>31</v>
+        <v>123</v>
       </c>
       <c r="E158" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F158" t="n">
-        <v>34</v>
+        <v>146</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>READSBORO</t>
+          <t>READING</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>BENNINGTON-1</t>
+          <t>WINDSOR-5</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>BENNINGTON_</t>
+          <t>WINDSOR_</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E159" t="n">
         <v>0</v>
       </c>
       <c r="F159" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>RICHFORD</t>
+          <t>READSBORO</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>FRANKLIN-5</t>
+          <t>BENNINGTON-1</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>FRANKLIN_</t>
+          <t>BENNINGTON_</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="E160" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F160" t="n">
-        <v>115</v>
+        <v>38</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>RICHMOND</t>
+          <t>RICHFORD</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>CHITTENDEN 1</t>
+          <t>FRANKLIN-5</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>CHITTENDEN-SOUTHEAST_</t>
+          <t>FRANKLIN_</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="E161" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F161" t="n">
-        <v>68</v>
+        <v>115</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>RIPTON</t>
+          <t>RICHMOND</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ADDISON-2</t>
+          <t>CHITTENDEN 1</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>ADDISON_</t>
+          <t>CHITTENDEN-SOUTHEAST_</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="E162" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F162" t="n">
-        <v>21</v>
+        <v>68</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ROCHESTER</t>
+          <t>RIPTON</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>WINDSOR ADDISON</t>
+          <t>ADDISON-2</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4651,154 +4651,154 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="E163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F163" t="n">
-        <v>41</v>
+        <v>21</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ROCKINGHAM</t>
+          <t>ROCHESTER</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>WINDHAM-3</t>
+          <t>WINDSOR ADDISON</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>WINDHAM_</t>
+          <t>ADDISON_</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>71</v>
+        <v>39</v>
       </c>
       <c r="E164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F164" t="n">
-        <v>84</v>
+        <v>41</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ROXBURY</t>
+          <t>ROCKINGHAM</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ORANGE WASHINGTON ADDISON</t>
+          <t>WINDHAM-3</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>WASHINGTON_</t>
+          <t>WINDHAM_</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="E165" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F165" t="n">
-        <v>43</v>
+        <v>84</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>ROYALTON</t>
+          <t>ROXBURY</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>WINDSOR ORANGE 1</t>
+          <t>ORANGE WASHINGTON ADDISON</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>WINDSOR_</t>
+          <t>WASHINGTON_</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>88</v>
+        <v>36</v>
       </c>
       <c r="E166" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F166" t="n">
-        <v>111</v>
+        <v>43</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>RUPERT</t>
+          <t>ROYALTON</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>RUTLAND BENNINGTON</t>
+          <t>WINDSOR ORANGE 1</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>BENNINGTON_</t>
+          <t>WINDSOR_</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="E167" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F167" t="n">
-        <v>40</v>
+        <v>111</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>RUTLAND CITY</t>
+          <t>RUPERT</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>RUTLAND-4, RUTLAND-5, RUTLAND-6, RUTLAND-7</t>
+          <t>RUTLAND BENNINGTON</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>RUTLAND_</t>
+          <t>BENNINGTON_</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>401</v>
+        <v>35</v>
       </c>
       <c r="E168" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F168" t="n">
-        <v>450</v>
+        <v>40</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>RUTLAND TOWN</t>
+          <t>RUTLAND CITY</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>RUTLAND-2, RUTLAND-4</t>
+          <t>RUTLAND-4, RUTLAND-5, RUTLAND-6, RUTLAND-7</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4807,76 +4807,76 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>175</v>
+        <v>401</v>
       </c>
       <c r="E169" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F169" t="n">
-        <v>187</v>
+        <v>450</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>RYEGATE</t>
+          <t>RUTLAND TOWN</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>CALEDONIA 1</t>
+          <t>RUTLAND-2, RUTLAND-4</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>CALEDONIA_</t>
+          <t>RUTLAND_</t>
         </is>
       </c>
       <c r="D170" t="n">
-        <v>47</v>
+        <v>175</v>
       </c>
       <c r="E170" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F170" t="n">
-        <v>57</v>
+        <v>187</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SAINT ALBANS CITY</t>
+          <t>RYEGATE</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>FRANKLIN-3, FRANKLIN-8</t>
+          <t>CALEDONIA 1</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>FRANKLIN_</t>
+          <t>CALEDONIA_</t>
         </is>
       </c>
       <c r="D171" t="n">
-        <v>151</v>
+        <v>47</v>
       </c>
       <c r="E171" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F171" t="n">
-        <v>184</v>
+        <v>57</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SAINT ALBANS TOWN</t>
+          <t>SAINT ALBANS CITY</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>FRANKLIN-2, FRANKLIN-8</t>
+          <t>FRANKLIN-3, FRANKLIN-8</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -4885,128 +4885,128 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>234</v>
+        <v>151</v>
       </c>
       <c r="E172" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F172" t="n">
-        <v>267</v>
+        <v>184</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SAINT GEORGE</t>
+          <t>SAINT ALBANS TOWN</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>CHITTENDEN-7</t>
+          <t>FRANKLIN-2, FRANKLIN-8</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>CHITTENDEN-SOUTHEAST_</t>
+          <t>FRANKLIN_</t>
         </is>
       </c>
       <c r="D173" t="n">
-        <v>22</v>
+        <v>234</v>
       </c>
       <c r="E173" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="F173" t="n">
-        <v>24</v>
+        <v>267</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SAINT JOHNSBURY</t>
+          <t>SAINT GEORGE</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>CALEDONIA ESSEX</t>
+          <t>CHITTENDEN-7</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>CALEDONIA_</t>
+          <t>CHITTENDEN-SOUTHEAST_</t>
         </is>
       </c>
       <c r="D174" t="n">
-        <v>365</v>
+        <v>22</v>
       </c>
       <c r="E174" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F174" t="n">
-        <v>425</v>
+        <v>24</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SALISBURY</t>
+          <t>SAINT JOHNSBURY</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ADDISON-2</t>
+          <t>CALEDONIA ESSEX</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>ADDISON_</t>
+          <t>CALEDONIA_</t>
         </is>
       </c>
       <c r="D175" t="n">
-        <v>37</v>
+        <v>365</v>
       </c>
       <c r="E175" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F175" t="n">
-        <v>44</v>
+        <v>425</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SANDGATE</t>
+          <t>SALISBURY</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>BENNINGTON-4</t>
+          <t>ADDISON-2</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>BENNINGTON_</t>
+          <t>ADDISON_</t>
         </is>
       </c>
       <c r="D176" t="n">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="E176" t="n">
         <v>0</v>
       </c>
       <c r="F176" t="n">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SEARSBURG</t>
+          <t>SANDGATE</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>BENNINGTON-1</t>
+          <t>BENNINGTON-4</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5015,24 +5015,24 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
       </c>
       <c r="F177" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SHAFTSBURY</t>
+          <t>SEARSBURG</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>BENNINGTON-3</t>
+          <t>BENNINGTON-1</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5041,1212 +5041,1212 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>189</v>
+        <v>9</v>
       </c>
       <c r="E178" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F178" t="n">
-        <v>219</v>
+        <v>10</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SHARON</t>
+          <t>SHAFTSBURY</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>WINDSOR ORANGE 2</t>
+          <t>BENNINGTON-3</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>WINDSOR_</t>
+          <t>BENNINGTON_</t>
         </is>
       </c>
       <c r="D179" t="n">
-        <v>46</v>
+        <v>189</v>
       </c>
       <c r="E179" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F179" t="n">
-        <v>51</v>
+        <v>219</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SHEFFIELD</t>
+          <t>SHARON</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>CALEDONIA 3</t>
+          <t>WINDSOR ORANGE 2</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ORLEANS_</t>
+          <t>WINDSOR_</t>
         </is>
       </c>
       <c r="D180" t="n">
+        <v>46</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" t="n">
         <v>51</v>
-      </c>
-      <c r="E180" t="n">
-        <v>5</v>
-      </c>
-      <c r="F180" t="n">
-        <v>63</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SHELBURNE</t>
+          <t>SHEFFIELD</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>CHITTENDEN-6, CHITTENDEN-7</t>
+          <t>CALEDONIA 3</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>CHITTENDEN-SOUTHEAST_</t>
+          <t>ORLEANS_</t>
         </is>
       </c>
       <c r="D181" t="n">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="E181" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F181" t="n">
-        <v>198</v>
+        <v>63</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SHELDON</t>
+          <t>SHELBURNE</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>FRANKLIN-4</t>
+          <t>CHITTENDEN-6, CHITTENDEN-7</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>FRANKLIN_</t>
+          <t>CHITTENDEN-SOUTHEAST_</t>
         </is>
       </c>
       <c r="D182" t="n">
-        <v>80</v>
+        <v>169</v>
       </c>
       <c r="E182" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F182" t="n">
-        <v>87</v>
+        <v>198</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>SHOREHAM</t>
+          <t>SHELDON</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ADDISON RUTLAND</t>
+          <t>FRANKLIN-4</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ADDISON_</t>
+          <t>FRANKLIN_</t>
         </is>
       </c>
       <c r="D183" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E183" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F183" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>SHREWSBURY</t>
+          <t>SHOREHAM</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>RUTLAND WINDSOR</t>
+          <t>ADDISON RUTLAND</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>RUTLAND_</t>
+          <t>ADDISON_</t>
         </is>
       </c>
       <c r="D184" t="n">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="E184" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F184" t="n">
-        <v>48</v>
+        <v>84</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>SOUTH BURLINGTON</t>
+          <t>SHREWSBURY</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>CHITTENDEN-10, CHITTENDEN-11, CHITTENDEN-12, CHITTENDEN-8, CHITTENDEN-9</t>
+          <t>RUTLAND WINDSOR</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>CHITTENDEN-SOUTHEAST_</t>
+          <t>RUTLAND_</t>
         </is>
       </c>
       <c r="D185" t="n">
-        <v>380</v>
+        <v>45</v>
       </c>
       <c r="E185" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F185" t="n">
-        <v>449</v>
+        <v>48</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SOUTH HERO</t>
+          <t>SOUTH BURLINGTON</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>GRAND ISLE CHITTENDEN</t>
+          <t>CHITTENDEN-10, CHITTENDEN-11, CHITTENDEN-12, CHITTENDEN-8, CHITTENDEN-9</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>GRAND ISLE_</t>
+          <t>CHITTENDEN-SOUTHEAST_</t>
         </is>
       </c>
       <c r="D186" t="n">
-        <v>99</v>
+        <v>380</v>
       </c>
       <c r="E186" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F186" t="n">
-        <v>109</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SPRINGFIELD</t>
+          <t>SOUTH HERO</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>WINDSOR-3</t>
+          <t>GRAND ISLE CHITTENDEN</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>WINDSOR_</t>
+          <t>GRAND ISLE_</t>
         </is>
       </c>
       <c r="D187" t="n">
-        <v>376</v>
+        <v>99</v>
       </c>
       <c r="E187" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F187" t="n">
-        <v>420</v>
+        <v>109</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>STAMFORD</t>
+          <t>SPRINGFIELD</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>BENNINGTON-1</t>
+          <t>WINDSOR-3</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>BENNINGTON_</t>
+          <t>WINDSOR_</t>
         </is>
       </c>
       <c r="D188" t="n">
-        <v>21</v>
+        <v>376</v>
       </c>
       <c r="E188" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F188" t="n">
-        <v>31</v>
+        <v>420</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>STANNARD</t>
+          <t>STAMFORD</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>CALEDONIA 2</t>
+          <t>BENNINGTON-1</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>CALEDONIA_</t>
+          <t>BENNINGTON_</t>
         </is>
       </c>
       <c r="D189" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E189" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F189" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>STARKSBORO</t>
+          <t>STANNARD</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ADDISON-4</t>
+          <t>CALEDONIA 2</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>ADDISON_</t>
+          <t>CALEDONIA_</t>
         </is>
       </c>
       <c r="D190" t="n">
-        <v>76</v>
+        <v>10</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F190" t="n">
-        <v>89</v>
+        <v>12</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>STATE WIDE</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr"/>
-      <c r="C191" t="inlineStr"/>
+          <t>STARKSBORO</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>ADDISON-4</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ADDISON_</t>
+        </is>
+      </c>
       <c r="D191" t="n">
-        <v>19961</v>
+        <v>76</v>
       </c>
       <c r="E191" t="n">
-        <v>586</v>
+        <v>0</v>
       </c>
       <c r="F191" t="n">
-        <v>22753</v>
+        <v>89</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>STOCKBRIDGE</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>WINDSOR ADDISON</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>WINDSOR_</t>
-        </is>
-      </c>
+          <t>STATE WIDE</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr"/>
       <c r="D192" t="n">
-        <v>26</v>
+        <v>20022</v>
       </c>
       <c r="E192" t="n">
-        <v>0</v>
+        <v>587</v>
       </c>
       <c r="F192" t="n">
-        <v>28</v>
+        <v>22824</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>STOWE</t>
+          <t>STOCKBRIDGE</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>LAMOILLE WASHINGTON, LAMOILLE-1</t>
+          <t>WINDSOR ADDISON</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>WASHINGTON_</t>
+          <t>WINDSOR_</t>
         </is>
       </c>
       <c r="D193" t="n">
-        <v>64</v>
+        <v>26</v>
       </c>
       <c r="E193" t="n">
         <v>0</v>
       </c>
       <c r="F193" t="n">
-        <v>77</v>
+        <v>28</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>STRAFFORD</t>
+          <t>STOWE</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>WINDSOR ORANGE 2</t>
+          <t>LAMOILLE WASHINGTON, LAMOILLE-1</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ORANGE_</t>
+          <t>WASHINGTON_</t>
         </is>
       </c>
       <c r="D194" t="n">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="E194" t="n">
         <v>0</v>
       </c>
       <c r="F194" t="n">
-        <v>17</v>
+        <v>77</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>STRATTON</t>
+          <t>STRAFFORD</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>WINDHAM-2</t>
+          <t>WINDSOR ORANGE 2</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>BENNINGTON_</t>
+          <t>ORANGE_</t>
         </is>
       </c>
       <c r="D195" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E195" t="n">
         <v>0</v>
       </c>
       <c r="F195" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SUDBURY</t>
+          <t>STRATTON</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ADDISON RUTLAND</t>
+          <t>WINDHAM-2</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>RUTLAND_</t>
+          <t>BENNINGTON_</t>
         </is>
       </c>
       <c r="D196" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E196" t="n">
         <v>0</v>
       </c>
       <c r="F196" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SUNDERLAND</t>
+          <t>SUDBURY</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>BENNINGTON-3, BENNINGTON-4</t>
+          <t>ADDISON RUTLAND</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>BENNINGTON_</t>
+          <t>RUTLAND_</t>
         </is>
       </c>
       <c r="D197" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E197" t="n">
         <v>0</v>
       </c>
       <c r="F197" t="n">
-        <v>43</v>
+        <v>23</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SUTTON</t>
+          <t>SUNDERLAND</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>CALEDONIA 3</t>
+          <t>BENNINGTON-3, BENNINGTON-4</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>ORLEANS_</t>
+          <t>BENNINGTON_</t>
         </is>
       </c>
       <c r="D198" t="n">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="E198" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F198" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SWANTON</t>
+          <t>SUTTON</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>FRANKLIN-4</t>
+          <t>CALEDONIA 3</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>FRANKLIN_</t>
+          <t>ORLEANS_</t>
         </is>
       </c>
       <c r="D199" t="n">
-        <v>227</v>
+        <v>66</v>
       </c>
       <c r="E199" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F199" t="n">
-        <v>256</v>
+        <v>78</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>THETFORD</t>
+          <t>SWANTON</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>WINDSOR ORANGE 2</t>
+          <t>FRANKLIN-4</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>WINDSOR_</t>
+          <t>FRANKLIN_</t>
         </is>
       </c>
       <c r="D200" t="n">
-        <v>48</v>
+        <v>227</v>
       </c>
       <c r="E200" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F200" t="n">
-        <v>54</v>
+        <v>256</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TINMOUTH</t>
+          <t>THETFORD</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>RUTLAND BENNINGTON</t>
+          <t>WINDSOR ORANGE 2</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>RUTLAND_</t>
+          <t>WINDSOR_</t>
         </is>
       </c>
       <c r="D201" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="E201" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F201" t="n">
-        <v>37</v>
+        <v>54</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>TOPSHAM</t>
+          <t>TINMOUTH</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ORANGE CALEDONIA</t>
+          <t>RUTLAND BENNINGTON</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>ORANGE_</t>
+          <t>RUTLAND_</t>
         </is>
       </c>
       <c r="D202" t="n">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="E202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F202" t="n">
-        <v>114</v>
+        <v>37</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TOWNSHEND</t>
+          <t>TOPSHAM</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>WINDHAM-5</t>
+          <t>ORANGE CALEDONIA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>WINDHAM_</t>
+          <t>ORANGE_</t>
         </is>
       </c>
       <c r="D203" t="n">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="E203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F203" t="n">
-        <v>40</v>
+        <v>114</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>TROY</t>
+          <t>TOWNSHEND</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ORLEANS LAMOILLE</t>
+          <t>WINDHAM-5</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>ORLEANS_</t>
+          <t>WINDHAM_</t>
         </is>
       </c>
       <c r="D204" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="E204" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F204" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>TUNBRIDGE</t>
+          <t>TROY</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>WINDSOR ORANGE 1</t>
+          <t>ORLEANS LAMOILLE</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>ORANGE_</t>
+          <t>ORLEANS_</t>
         </is>
       </c>
       <c r="D205" t="n">
-        <v>105</v>
+        <v>50</v>
       </c>
       <c r="E205" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F205" t="n">
-        <v>127</v>
+        <v>55</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>UNDERHILL</t>
+          <t>TUNBRIDGE</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>CHITTENDEN 3</t>
+          <t>WINDSOR ORANGE 1</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>CHITTENDEN-SOUTHEAST_</t>
+          <t>ORANGE_</t>
         </is>
       </c>
       <c r="D206" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E206" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F206" t="n">
-        <v>110</v>
+        <v>127</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>VERGENNES</t>
+          <t>UNDERHILL</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>ADDISON-3</t>
+          <t>CHITTENDEN 3</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>ADDISON_</t>
+          <t>CHITTENDEN-SOUTHEAST_</t>
         </is>
       </c>
       <c r="D207" t="n">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="E207" t="n">
         <v>0</v>
       </c>
       <c r="F207" t="n">
-        <v>124</v>
+        <v>110</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>VERNON</t>
+          <t>VERGENNES</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>WINDHAM-1</t>
+          <t>ADDISON-3</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>WINDHAM_</t>
+          <t>ADDISON_</t>
         </is>
       </c>
       <c r="D208" t="n">
-        <v>61</v>
+        <v>118</v>
       </c>
       <c r="E208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F208" t="n">
-        <v>75</v>
+        <v>124</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>VERSHIRE</t>
+          <t>VERNON</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ORANGE-1</t>
+          <t>WINDHAM-1</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>ORANGE_</t>
+          <t>WINDHAM_</t>
         </is>
       </c>
       <c r="D209" t="n">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="E209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F209" t="n">
-        <v>41</v>
+        <v>75</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>VICTORY</t>
+          <t>VERSHIRE</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ESSEX CALEDONIA</t>
+          <t>ORANGE-1</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>ESSEX_</t>
+          <t>ORANGE_</t>
         </is>
       </c>
       <c r="D210" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="E210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F210" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>WAITSFIELD</t>
+          <t>VICTORY</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>WASHINGTON-2</t>
+          <t>ESSEX CALEDONIA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>WASHINGTON_</t>
+          <t>ESSEX_</t>
         </is>
       </c>
       <c r="D211" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E211" t="n">
         <v>1</v>
       </c>
       <c r="F211" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>WALDEN</t>
+          <t>WAITSFIELD</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>CALEDONIA 2</t>
+          <t>WASHINGTON-2</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>CALEDONIA_</t>
+          <t>WASHINGTON_</t>
         </is>
       </c>
       <c r="D212" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E212" t="n">
         <v>1</v>
       </c>
       <c r="F212" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>WALLINGFORD</t>
+          <t>WALDEN</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>RUTLAND-2</t>
+          <t>CALEDONIA 2</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>RUTLAND_</t>
+          <t>CALEDONIA_</t>
         </is>
       </c>
       <c r="D213" t="n">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="E213" t="n">
         <v>1</v>
       </c>
       <c r="F213" t="n">
-        <v>77</v>
+        <v>42</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>WALTHAM</t>
+          <t>WALLINGFORD</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ADDISON-3</t>
+          <t>RUTLAND-2</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>ADDISON_</t>
+          <t>RUTLAND_</t>
         </is>
       </c>
       <c r="D214" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="E214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F214" t="n">
-        <v>33</v>
+        <v>77</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>WARDSBORO</t>
+          <t>WALTHAM</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>WINDHAM-2</t>
+          <t>ADDISON-3</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>WINDHAM_</t>
+          <t>ADDISON_</t>
         </is>
       </c>
       <c r="D215" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F215" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>WARREN</t>
+          <t>WARDSBORO</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>WASHINGTON-2</t>
+          <t>WINDHAM-2</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>WASHINGTON_</t>
+          <t>WINDHAM_</t>
         </is>
       </c>
       <c r="D216" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F216" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>WASHINGTON</t>
+          <t>WARREN</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ORANGE-1</t>
+          <t>WASHINGTON-2</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>ORANGE_</t>
+          <t>WASHINGTON_</t>
         </is>
       </c>
       <c r="D217" t="n">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="E217" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F217" t="n">
-        <v>82</v>
+        <v>35</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>WATERBURY</t>
+          <t>WASHINGTON</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>WASHINGTON CHITTENDEN</t>
+          <t>ORANGE-1</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>WASHINGTON_</t>
+          <t>ORANGE_</t>
         </is>
       </c>
       <c r="D218" t="n">
+        <v>71</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+      <c r="F218" t="n">
         <v>82</v>
-      </c>
-      <c r="E218" t="n">
-        <v>3</v>
-      </c>
-      <c r="F218" t="n">
-        <v>97</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>WATERFORD</t>
+          <t>WATERBURY</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>CALEDONIA 1</t>
+          <t>WASHINGTON CHITTENDEN</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>CALEDONIA_</t>
+          <t>WASHINGTON_</t>
         </is>
       </c>
       <c r="D219" t="n">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="E219" t="n">
         <v>3</v>
       </c>
       <c r="F219" t="n">
-        <v>118</v>
+        <v>97</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>WATERVILLE</t>
+          <t>WATERFORD</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>LAMOILLE-3</t>
+          <t>CALEDONIA 1</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>LAMOILLE_</t>
+          <t>CALEDONIA_</t>
         </is>
       </c>
       <c r="D220" t="n">
-        <v>39</v>
+        <v>94</v>
       </c>
       <c r="E220" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F220" t="n">
-        <v>41</v>
+        <v>118</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>WEATHERSFIELD</t>
+          <t>WATERVILLE</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>WINDSOR-2</t>
+          <t>LAMOILLE-3</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>WINDSOR_</t>
+          <t>LAMOILLE_</t>
         </is>
       </c>
       <c r="D221" t="n">
-        <v>173</v>
+        <v>39</v>
       </c>
       <c r="E221" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F221" t="n">
-        <v>200</v>
+        <v>41</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>WELLS</t>
+          <t>WEATHERSFIELD</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>RUTLAND BENNINGTON, RUTLAND-1</t>
+          <t>WINDSOR-2</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>RUTLAND_</t>
+          <t>WINDSOR_</t>
         </is>
       </c>
       <c r="D222" t="n">
-        <v>60</v>
+        <v>173</v>
       </c>
       <c r="E222" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F222" t="n">
-        <v>64</v>
+        <v>200</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>WEST FAIRLEE</t>
+          <t>WELLS</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>ORANGE-2</t>
+          <t>RUTLAND BENNINGTON, RUTLAND-1</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>ORANGE_</t>
+          <t>RUTLAND_</t>
         </is>
       </c>
       <c r="D223" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="E223" t="n">
         <v>0</v>
       </c>
       <c r="F223" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>WEST HAVEN</t>
+          <t>WEST FAIRLEE</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>RUTLAND-10</t>
+          <t>ORANGE-2</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>RUTLAND_</t>
+          <t>ORANGE_</t>
         </is>
       </c>
       <c r="D224" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E224" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F224" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>WEST RUTLAND</t>
+          <t>WEST HAVEN</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>RUTLAND-2</t>
+          <t>RUTLAND-10</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6255,584 +6255,610 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>86</v>
+        <v>7</v>
       </c>
       <c r="E225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F225" t="n">
-        <v>94</v>
+        <v>14</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>WEST WINDSOR</t>
+          <t>WEST RUTLAND</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>WINDSOR-1</t>
+          <t>RUTLAND-2</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>WINDSOR_</t>
+          <t>RUTLAND_</t>
         </is>
       </c>
       <c r="D226" t="n">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="E226" t="n">
         <v>1</v>
       </c>
       <c r="F226" t="n">
-        <v>49</v>
+        <v>94</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>WESTFIELD</t>
+          <t>WEST WINDSOR</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>ORLEANS LAMOILLE</t>
+          <t>WINDSOR-1</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>ORLEANS_</t>
+          <t>WINDSOR_</t>
         </is>
       </c>
       <c r="D227" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="E227" t="n">
         <v>1</v>
       </c>
       <c r="F227" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>WESTFORD</t>
+          <t>WESTFIELD</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>CHITTENDEN-25</t>
+          <t>ORLEANS LAMOILLE</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>CHITTENDEN-NORTH_</t>
+          <t>ORLEANS_</t>
         </is>
       </c>
       <c r="D228" t="n">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="E228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F228" t="n">
-        <v>65</v>
+        <v>34</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>WESTMINSTER</t>
+          <t>WESTFORD</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>WINDHAM-3</t>
+          <t>CHITTENDEN-25</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>WINDHAM_</t>
+          <t>CHITTENDEN-NORTH_</t>
         </is>
       </c>
       <c r="D229" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="E229" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F229" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>WESTMORE</t>
+          <t>WESTMINSTER</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>ORLEANS-3</t>
+          <t>WINDHAM-3</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>ORLEANS_</t>
+          <t>WINDHAM_</t>
         </is>
       </c>
       <c r="D230" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F230" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>WESTON</t>
+          <t>WESTMORE</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>WINDHAM WINDSOR BENNINGTON</t>
+          <t>ORLEANS-3</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>WINDSOR_</t>
+          <t>ORLEANS_</t>
         </is>
       </c>
       <c r="D231" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E231" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F231" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>WEYBRIDGE</t>
+          <t>WESTON</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>ADDISON-5</t>
+          <t>WINDHAM WINDSOR BENNINGTON</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>ADDISON_</t>
+          <t>WINDSOR_</t>
         </is>
       </c>
       <c r="D232" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E232" t="n">
         <v>0</v>
       </c>
       <c r="F232" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>WHEELOCK</t>
+          <t>WEYBRIDGE</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>CALEDONIA 3</t>
+          <t>ADDISON-5</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>CALEDONIA_</t>
+          <t>ADDISON_</t>
         </is>
       </c>
       <c r="D233" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="E233" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F233" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>WHITING</t>
+          <t>WHEELOCK</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>ADDISON RUTLAND</t>
+          <t>CALEDONIA 3</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>ADDISON_</t>
+          <t>CALEDONIA_</t>
         </is>
       </c>
       <c r="D234" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="E234" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F234" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>WHITINGHAM</t>
+          <t>WHITING</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>WINDHAM-6</t>
+          <t>ADDISON RUTLAND</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>WINDHAM_</t>
+          <t>ADDISON_</t>
         </is>
       </c>
       <c r="D235" t="n">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="E235" t="n">
         <v>0</v>
       </c>
       <c r="F235" t="n">
-        <v>56</v>
+        <v>25</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>WILLIAMSTOWN</t>
+          <t>WHITINGHAM</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>ORANGE-3, WASHINGTON ORANGE</t>
+          <t>WINDHAM-6</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>ORANGE_</t>
+          <t>WINDHAM_</t>
         </is>
       </c>
       <c r="D236" t="n">
-        <v>128</v>
+        <v>53</v>
       </c>
       <c r="E236" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F236" t="n">
-        <v>144</v>
+        <v>56</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>WILLISTON</t>
+          <t>WILLIAMSTOWN</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>CHITTENDEN 2, CHITTENDEN-8</t>
+          <t>ORANGE-3, WASHINGTON ORANGE</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>CHITTENDEN-SOUTHEAST_</t>
+          <t>ORANGE_</t>
         </is>
       </c>
       <c r="D237" t="n">
-        <v>292</v>
+        <v>128</v>
       </c>
       <c r="E237" t="n">
         <v>4</v>
       </c>
       <c r="F237" t="n">
-        <v>318</v>
+        <v>144</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>WILMINGTON</t>
+          <t>WILLISTON</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>WINDHAM-6</t>
+          <t>CHITTENDEN 2, CHITTENDEN-8</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>BENNINGTON_</t>
+          <t>CHITTENDEN-SOUTHEAST_</t>
         </is>
       </c>
       <c r="D238" t="n">
-        <v>34</v>
+        <v>292</v>
       </c>
       <c r="E238" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F238" t="n">
-        <v>38</v>
+        <v>318</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>WINDHAM</t>
+          <t>WILMINGTON</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>WINDSOR WINDHAM</t>
+          <t>WINDHAM-6</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>WINDHAM_</t>
+          <t>BENNINGTON_</t>
         </is>
       </c>
       <c r="D239" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="E239" t="n">
         <v>0</v>
       </c>
       <c r="F239" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>WINDSOR</t>
+          <t>WINDHAM</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>WINDSOR-1</t>
+          <t>WINDSOR WINDHAM</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>WINDSOR_</t>
+          <t>WINDHAM_</t>
         </is>
       </c>
       <c r="D240" t="n">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="E240" t="n">
         <v>0</v>
       </c>
       <c r="F240" t="n">
-        <v>94</v>
+        <v>10</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>WINHALL</t>
+          <t>WINDSOR</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>WINDHAM WINDSOR BENNINGTON</t>
+          <t>WINDSOR-1</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>BENNINGTON_</t>
+          <t>WINDSOR_</t>
         </is>
       </c>
       <c r="D241" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E241" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F241" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>WINOOSKI</t>
+          <t>WINHALL</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>CHITTENDEN-21</t>
+          <t>WINDHAM WINDSOR BENNINGTON</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>CHITTENDEN-CENTRAL_</t>
+          <t>BENNINGTON_</t>
         </is>
       </c>
       <c r="D242" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="E242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F242" t="n">
-        <v>62</v>
+        <v>85</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>WOLCOTT</t>
+          <t>WINOOSKI</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>LAMOILLE-2</t>
+          <t>CHITTENDEN-21</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>LAMOILLE_</t>
+          <t>CHITTENDEN-CENTRAL_</t>
         </is>
       </c>
       <c r="D243" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="E243" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F243" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>WOODBURY</t>
+          <t>WOLCOTT</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>LAMOILLE WASHINGTON</t>
+          <t>LAMOILLE-2</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>WASHINGTON_</t>
+          <t>LAMOILLE_</t>
         </is>
       </c>
       <c r="D244" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F244" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>WOODFORD</t>
+          <t>WOODBURY</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>BENNINGTON-1</t>
+          <t>LAMOILLE WASHINGTON</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>BENNINGTON_</t>
+          <t>WASHINGTON_</t>
         </is>
       </c>
       <c r="D245" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="E245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F245" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>WOODSTOCK</t>
+          <t>WOODFORD</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>WINDSOR-5</t>
+          <t>BENNINGTON-1</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>WINDSOR_</t>
+          <t>BENNINGTON_</t>
         </is>
       </c>
       <c r="D246" t="n">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="E246" t="n">
         <v>0</v>
       </c>
       <c r="F246" t="n">
-        <v>139</v>
+        <v>25</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
+          <t>WOODSTOCK</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>WINDSOR-5</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>WINDSOR_</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
+        <v>112</v>
+      </c>
+      <c r="E247" t="n">
+        <v>0</v>
+      </c>
+      <c r="F247" t="n">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
           <t>WORCESTER</t>
         </is>
       </c>
-      <c r="B247" t="inlineStr">
+      <c r="B248" t="inlineStr">
         <is>
           <t>LAMOILLE WASHINGTON</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr">
+      <c r="C248" t="inlineStr">
         <is>
           <t>WASHINGTON_</t>
         </is>
       </c>
-      <c r="D247" t="n">
+      <c r="D248" t="n">
         <v>53</v>
       </c>
-      <c r="E247" t="n">
+      <c r="E248" t="n">
         <v>2</v>
       </c>
-      <c r="F247" t="n">
+      <c r="F248" t="n">
         <v>60</v>
       </c>
     </row>
